--- a/MenstruAccion/cuanto_cuesta_menstruar/2026 Marzo/Fuentes/serie_inflacion.xlsx
+++ b/MenstruAccion/cuanto_cuesta_menstruar/2026 Marzo/Fuentes/serie_inflacion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\espin\Documents\2. Militancia\Ecofeminita\EcoFemiData\MenstruAccion\cuanto_cuesta_menstruar\2025 Septiembre\Fuentes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\espin\Documents\2. Militancia\Ecofeminita\EcoFemiData\MenstruAccion\cuanto_cuesta_menstruar\2026 Marzo\Fuentes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF40723E-A6D7-484D-AD23-EFAF71C43E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D93D6C3-E148-43E0-9428-97CD6332E35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -202,7 +202,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -222,9 +222,6 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="20" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="22">
@@ -337,6 +334,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Variación mensual IPC Nacional"/>
@@ -424,6 +422,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Variación mensual IPC Nacional"/>
@@ -753,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1838,7 +1837,7 @@
       <c r="B75" s="16">
         <v>8585.6077999999998</v>
       </c>
-      <c r="C75" s="20">
+      <c r="C75" s="17">
         <v>9318.2093000000004</v>
       </c>
       <c r="D75" s="17">
@@ -1852,7 +1851,7 @@
       <c r="B76" s="16">
         <v>8714.4871000000003</v>
       </c>
-      <c r="C76" s="20">
+      <c r="C76" s="17">
         <v>9365.3120999999992</v>
       </c>
       <c r="D76" s="17">
@@ -1866,7 +1865,7 @@
       <c r="B77" s="16">
         <v>8855.5681000000004</v>
       </c>
-      <c r="C77" s="20">
+      <c r="C77" s="17">
         <v>9418.0825999999997</v>
       </c>
       <c r="D77" s="17">
@@ -1880,7 +1879,7 @@
       <c r="B78" s="16">
         <v>9023.973</v>
       </c>
-      <c r="C78" s="20">
+      <c r="C78" s="17">
         <v>9596.7407000000003</v>
       </c>
       <c r="D78" s="17">
@@ -1894,7 +1893,7 @@
       <c r="B79" s="16">
         <v>9193.2440999999999</v>
       </c>
-      <c r="C79" s="20">
+      <c r="C79" s="17">
         <v>9729.0210999999999</v>
       </c>
       <c r="D79" s="17">
@@ -1905,19 +1904,105 @@
       <c r="A80" s="1">
         <v>45901</v>
       </c>
-      <c r="B80" s="18">
+      <c r="B80" s="16">
         <v>9384.0921999999991</v>
       </c>
-      <c r="C80" s="20">
+      <c r="C80" s="17">
         <v>9910.1309999999994</v>
       </c>
-      <c r="D80" s="19">
+      <c r="D80" s="17">
         <v>10648.1896</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="B81" s="16"/>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B81" s="9">
+        <v>9603.8623000000007</v>
+      </c>
+      <c r="C81" s="8">
+        <v>10136.6605</v>
+      </c>
+      <c r="D81" s="8">
+        <v>10842.673000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B82" s="9">
+        <v>9841.3580999999995</v>
+      </c>
+      <c r="C82" s="8">
+        <v>10421.9128</v>
+      </c>
+      <c r="D82" s="8">
+        <v>11102.611800000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B83" s="9">
+        <v>10121.371499999999</v>
+      </c>
+      <c r="C83" s="8">
+        <v>10748.4071</v>
+      </c>
+      <c r="D83" s="8">
+        <v>11335.1633</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46023</v>
+      </c>
+      <c r="B84" s="9">
+        <v>10413.0309</v>
+      </c>
+      <c r="C84" s="8">
+        <v>11251.116599999999</v>
+      </c>
+      <c r="D84" s="8">
+        <v>11600.3264</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46054</v>
+      </c>
+      <c r="B85" s="9">
+        <v>10714.6255</v>
+      </c>
+      <c r="C85" s="8">
+        <v>11624.980799999999</v>
+      </c>
+      <c r="D85" s="8">
+        <v>11886.5002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B86" s="9">
+        <v>11077.060799999999</v>
+      </c>
+      <c r="C86" s="8">
+        <v>12014.7</v>
+      </c>
+      <c r="D86" s="8">
+        <v>12201.311600000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="1"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
